--- a/artfynd/S 2590-2025 artfynd.xlsx
+++ b/artfynd/S 2590-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381657</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746018</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746220</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738380</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738381</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738383</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1479,6 +1519,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746197</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548193</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381720</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738385</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746234</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381309</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2114,6 +2184,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527501</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379079</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2324,6 +2404,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381396</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2429,6 +2514,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381435</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2534,6 +2624,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381465</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2639,6 +2734,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381531</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2744,6 +2844,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381554</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2845,6 +2950,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746055</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2946,6 +3056,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746150</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3047,6 +3162,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746160</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3148,6 +3268,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746176</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3249,6 +3374,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746181</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3350,6 +3480,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746183</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3450,6 +3585,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746134</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3554,6 +3694,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61378955</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3658,6 +3803,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379082</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3758,6 +3908,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738378</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3858,6 +4013,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746124</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3959,6 +4119,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746142</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4067,6 +4232,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548230</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4172,6 +4342,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527890</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4277,6 +4452,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381184</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4382,6 +4562,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381534</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4487,6 +4672,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381558</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4592,6 +4782,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381723</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4696,6 +4891,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379091</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4796,6 +4996,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738379</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4896,6 +5101,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746128</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4996,6 +5206,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746167</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5096,6 +5311,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746196</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5196,6 +5416,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746214</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5300,6 +5525,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527447</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5400,6 +5630,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746237</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5500,6 +5735,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746040</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5604,6 +5844,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527514</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5708,6 +5953,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527561</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5812,6 +6062,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527648</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5916,6 +6171,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527875</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6020,6 +6280,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548306</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6124,6 +6389,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379080</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6228,6 +6498,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381163</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6328,6 +6603,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746028</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6428,6 +6708,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746052</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6528,6 +6813,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746038</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6632,6 +6922,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548293</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6732,6 +7027,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746032</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6843,6 +7143,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548265</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6948,6 +7253,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548048</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7053,6 +7363,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548147</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7158,6 +7473,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381315</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7263,6 +7583,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381322</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7368,6 +7693,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381618</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7473,6 +7803,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61378962</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7578,6 +7913,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379093</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7683,6 +8023,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381592</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7785,6 +8130,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746042</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7887,6 +8237,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746056</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7989,6 +8344,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746170</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8091,6 +8451,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746192</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8196,6 +8561,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548179</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8296,6 +8666,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381579</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8401,6 +8776,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381728</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8503,6 +8883,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746190</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8605,6 +8990,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73770578</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8706,6 +9096,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548215</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8811,6 +9206,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54547951</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8916,6 +9316,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61378945</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9021,6 +9426,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61378960</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9126,6 +9536,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379095</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9228,6 +9643,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746035</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9330,6 +9750,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746059</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9432,6 +9857,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746191</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9534,6 +9964,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746245</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9645,6 +10080,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132494471</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9750,6 +10190,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548104</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9855,6 +10300,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548136</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9960,8 +10410,105 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381611</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>